--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepFloatFee.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepFloatFee.xlsx
@@ -82,11 +82,13 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -172,14 +174,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -489,31 +491,31 @@
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="14.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="8" customWidth="1"/>
     <col min="4" max="4" width="14.5" style="5" customWidth="1"/>
     <col min="5" max="16384" width="14.5" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepFloatFee.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepFloatFee.xlsx
@@ -21,12 +21,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>子产品代码*</t>
-  </si>
-  <si>
-    <t>产品名称*</t>
   </si>
   <si>
     <t>业务代码*</t>
@@ -487,24 +484,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="14.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="14.5" style="5"/>
+    <col min="1" max="1" width="14.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="14.5" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>2</v>
@@ -514,9 +511,6 @@
       </c>
       <c r="F1" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -533,37 +527,37 @@
   <sheetData>
     <row r="1" spans="1:1" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="38.25" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
